--- a/aq_files/0618.xlsx
+++ b/aq_files/0618.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,888 +413,533 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Q#</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Option C</t>
+          <t>Options (if MCQ)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Option D</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Answer</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Difficulty</t>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ELT stands for:</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Extract Load Transform</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Extract Log Transfer</t>
+          <t>What does HDFS stand for?</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Evaluate Load Transform</t>
+          <t>A) Hadoop Data File System B) Hadoop Distributed File System C) High Data File System D) Hybrid DFS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ETL transforms:</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Before load</t>
+          <t>One Word</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>After load</t>
+          <t>Which container platform is commonly used to deploy HDFS clusters?</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>During read</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Never</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ELT transforms:</t>
-        </is>
+      <c r="A4" t="n">
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Before load</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>After load</t>
+          <t>Which node stores actual data in HDFS?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>During extract</t>
+          <t>A) NameNode B) DataNode C) ResourceManager D) Client</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Never</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Big data prefers:</t>
-        </is>
+      <c r="A5" t="n">
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ETL</t>
+          <t>Scenario</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ELT</t>
+          <t>You need to scale storage in HDFS. What should you add?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Cloud systems commonly use:</t>
-        </is>
+      <c r="A6" t="n">
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ETL</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ELT</t>
+          <t>Which node manages metadata in HDFS?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>A) DataNode B) NameNode C) WorkerNode D) EdgeNode</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Traditional approach:</t>
-        </is>
+      <c r="A7" t="n">
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ETL</t>
+          <t>One Word</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ELT</t>
+          <t>Which file system command lists HDFS files?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>More scalable:</t>
-        </is>
+      <c r="A8" t="n">
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ETL</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ELT</t>
+          <t>Default block size in HDFS?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>A) 64MB B) 128MB C) 256MB D) 512MB</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Requires powerful warehouse:</t>
-        </is>
+      <c r="A9" t="n">
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ETL</t>
+          <t>Scenario</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ELT</t>
+          <t>Container fails for DataNode. Impact?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>More preprocessing needed:</t>
-        </is>
+      <c r="A10" t="n">
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ETL</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ELT</t>
+          <t>Replication factor ensures?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>A) Speed B) Fault tolerance C) Compression D) Security</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Stores raw data first:</t>
-        </is>
+      <c r="A11" t="n">
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ETL</t>
+          <t>One Word</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ELT</t>
+          <t>Configuration file for HDFS?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Uses data lakes heavily:</t>
-        </is>
+      <c r="A12" t="n">
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ETL</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ELT</t>
+          <t>Which port is commonly used by NameNode UI?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>A) 50070 B) 8080 C) 4040 D) 9000</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Faster at scale:</t>
-        </is>
+      <c r="A13" t="n">
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ETL</t>
+          <t>Scenario</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ELT</t>
+          <t>Need isolation of HDFS services. What helps?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Cost efficiency in cloud:</t>
-        </is>
+      <c r="A14" t="n">
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ETL</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ELT</t>
+          <t>Which command starts HDFS services?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>A) start-dfs.sh B) run-hdfs C) hdfs start D) init-hdfs</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Example ELT tool:</t>
-        </is>
+      <c r="A15" t="n">
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>One Word</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>Storage unit in HDFS?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A company loads raw JSON into a cloud warehouse and runs SQL transforms afterward for analytics. Which pattern?</t>
-        </is>
+      <c r="A16" t="n">
+        <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ETL</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ELT</t>
+          <t>Which tool orchestrates containers?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>A) Kubernetes B) Hadoop C) Hive D) Pig</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+          <t>MCQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Sensitive PII must be masked before any storage. Which pattern is safer?</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>ETL</t>
-        </is>
-      </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ELT</t>
+          <t>NameNode fails. What ensures recovery?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+          <t>Scenario-Based</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Which protocol HDFS uses?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>A) HTTP B) TCP/IP C) FTP D) SMTP</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>One Word</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Command to upload file to HDFS?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Data locality means?</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>A) Data near compute B) Remote storage C) Backup D) Encryption</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Compute is abundant in the warehouse and transformations are heavy SQL joins. Choose:</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ETL</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>ELT</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Legacy on-prem system with limited warehouse compute. Choose:</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>ETL</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>ELT</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Need near real-time dashboards with minimal preprocessing latency. Choose:</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ETL</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>ELT</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Strict governance requires validation before persistence. Choose:</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>ETL</t>
-        </is>
-      </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ELT</t>
+          <t>Need multi-node cluster locally. Solution?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
